--- a/literature-review/results/results_topic3.xlsx
+++ b/literature-review/results/results_topic3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\177020724\Documents\Studium\Thesis\Literature Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F0D683D-9D86-4210-A934-E4BCC8A2E88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9E7BAB-2CE6-4075-8748-F08555B53E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9420" yWindow="2436" windowWidth="22116" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -682,7 +682,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -707,9 +707,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
@@ -752,22 +749,10 @@
   </cellStyles>
   <dxfs count="17">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -807,6 +792,18 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -830,20 +827,20 @@
   <autoFilter ref="A2:O20" xr:uid="{0C5B4A38-1107-4982-A90D-0B53B8E3FDD5}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{D5837C41-A614-42A8-BD06-86F64680F0A2}" name="Index" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{81AE2D55-46F0-4224-8FAC-7F8CBAFBCD93}" name="Title" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{B374F111-5398-4F5C-9065-0C92E010DC0D}" name="Link" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{48D5B335-FEC3-45A1-B599-B37ADA8AB433}" name="Year" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{D517BB4A-F8D9-4A1A-8DAC-4ED55F73B7C5}" name="Domain" dataDxfId="4"/>
-    <tableColumn id="26" xr3:uid="{AE43902B-3019-413E-9DBE-7D4A1B1DBDAF}" name="Downstream tasks" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{61F9C5F7-950A-4F76-8C1A-F082BD1F88C8}" name="Type of problem(s) described" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{232E9CE2-4916-4233-BC07-E3E4A3A081B3}" name="Metrics used" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{5AA90D9C-1033-4A82-BC03-B93164FCC4C1}" name="Number of samples" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{A435D2FF-1331-4BD1-8F82-15A241B03852}" name="Labled/Unlabeled" dataDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{971C8B80-C108-40E3-9F62-320948DFCB84}" name="Learning Types mentioned" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{20BC529F-0800-446A-8F47-AC38727C0449}" name="Robustness testing" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{81AE2D55-46F0-4224-8FAC-7F8CBAFBCD93}" name="Title" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B374F111-5398-4F5C-9065-0C92E010DC0D}" name="Link" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{48D5B335-FEC3-45A1-B599-B37ADA8AB433}" name="Year" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{D517BB4A-F8D9-4A1A-8DAC-4ED55F73B7C5}" name="Domain" dataDxfId="10"/>
+    <tableColumn id="26" xr3:uid="{AE43902B-3019-413E-9DBE-7D4A1B1DBDAF}" name="Downstream tasks" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{61F9C5F7-950A-4F76-8C1A-F082BD1F88C8}" name="Type of problem(s) described" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{232E9CE2-4916-4233-BC07-E3E4A3A081B3}" name="Metrics used" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{5AA90D9C-1033-4A82-BC03-B93164FCC4C1}" name="Number of samples" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{A435D2FF-1331-4BD1-8F82-15A241B03852}" name="Labled/Unlabeled" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{971C8B80-C108-40E3-9F62-320948DFCB84}" name="Learning Types mentioned" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{20BC529F-0800-446A-8F47-AC38727C0449}" name="Robustness testing" dataDxfId="3"/>
     <tableColumn id="13" xr3:uid="{420767DF-8F51-47D1-A265-155E164F3FB4}" name="Models evaluated" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{390DCC4D-DF5A-48DA-B53C-DEAE2E383F23}" name="Amount of models tested" dataDxfId="0"/>
-    <tableColumn id="14" xr3:uid="{EA8AFE10-39EB-4529-8923-318C529A0A0C}" name="Comments" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{390DCC4D-DF5A-48DA-B53C-DEAE2E383F23}" name="Amount of models tested" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{EA8AFE10-39EB-4529-8923-318C529A0A0C}" name="Comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1137,24 +1134,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="31.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="31.1015625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="34" style="8" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" style="17" customWidth="1"/>
-    <col min="5" max="5" width="29.109375" customWidth="1"/>
-    <col min="6" max="6" width="42.33203125" customWidth="1"/>
-    <col min="7" max="7" width="28.5546875" customWidth="1"/>
-    <col min="8" max="10" width="20.5546875" customWidth="1"/>
-    <col min="11" max="11" width="25.88671875" customWidth="1"/>
-    <col min="12" max="12" width="26.33203125" customWidth="1"/>
-    <col min="13" max="13" width="22.88671875" customWidth="1"/>
-    <col min="14" max="14" width="28.44140625" style="21" customWidth="1"/>
-    <col min="15" max="15" width="20.5546875" customWidth="1"/>
+    <col min="3" max="3" width="23.3125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="7.68359375" style="16" customWidth="1"/>
+    <col min="5" max="5" width="29.1015625" customWidth="1"/>
+    <col min="6" max="6" width="42.3125" customWidth="1"/>
+    <col min="7" max="7" width="28.5234375" customWidth="1"/>
+    <col min="8" max="10" width="20.5234375" customWidth="1"/>
+    <col min="11" max="11" width="25.89453125" customWidth="1"/>
+    <col min="12" max="12" width="26.3125" customWidth="1"/>
+    <col min="13" max="13" width="22.89453125" customWidth="1"/>
+    <col min="14" max="14" width="28.41796875" style="20" customWidth="1"/>
+    <col min="15" max="15" width="20.5234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="18.3" x14ac:dyDescent="0.7">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -1170,10 +1167,10 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="23"/>
+      <c r="N1" s="22"/>
       <c r="O1" s="6"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1220,17 +1217,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="172.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9">
         <v>0</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="18">
         <v>2024</v>
       </c>
       <c r="E3" s="11" t="s">
@@ -1260,24 +1257,24 @@
       <c r="M3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N3" s="20">
+      <c r="N3" s="19">
         <v>15</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="16">
         <v>2024</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -1307,24 +1304,24 @@
       <c r="M4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="N4" s="18">
+      <c r="N4" s="17">
         <v>24</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:15" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" s="7" customFormat="1" ht="172.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="9">
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="18">
         <v>2024</v>
       </c>
       <c r="E5" s="11" t="s">
@@ -1354,24 +1351,24 @@
       <c r="M5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="N5" s="18">
+      <c r="N5" s="17">
         <v>15</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="17">
         <v>2024</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -1401,22 +1398,22 @@
       <c r="M6" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="N6" s="18" t="s">
+      <c r="N6" s="17" t="s">
         <v>74</v>
       </c>
       <c r="O6" s="3"/>
     </row>
-    <row r="7" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2">
         <v>4</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="19">
         <v>2024</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -1446,22 +1443,22 @@
       <c r="M7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N7" s="18">
+      <c r="N7" s="17">
         <v>3</v>
       </c>
       <c r="O7" s="3"/>
     </row>
-    <row r="8" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <v>2024</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -1491,22 +1488,22 @@
       <c r="M8" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="N8" s="18">
+      <c r="N8" s="17">
         <v>4</v>
       </c>
       <c r="O8" s="3"/>
     </row>
-    <row r="9" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2">
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="19">
         <v>2024</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -1536,24 +1533,24 @@
       <c r="M9" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="N9" s="18">
+      <c r="N9" s="17">
         <v>4</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2">
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <v>2024</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -1583,24 +1580,24 @@
       <c r="M10" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="N10" s="18">
+      <c r="N10" s="17">
         <v>3</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2">
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="19">
         <v>2024</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -1630,22 +1627,22 @@
       <c r="M11" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="N11" s="18">
+      <c r="N11" s="17">
         <v>4</v>
       </c>
       <c r="O11" s="3"/>
     </row>
-    <row r="12" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="158.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="17">
         <v>2024</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -1675,22 +1672,22 @@
       <c r="M12" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N12" s="18">
+      <c r="N12" s="17">
         <v>7</v>
       </c>
       <c r="O12" s="3"/>
     </row>
-    <row r="13" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2">
         <v>10</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="19">
         <v>2024</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -1720,22 +1717,22 @@
       <c r="M13" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="N13" s="18">
+      <c r="N13" s="17">
         <v>3</v>
       </c>
       <c r="O13" s="3"/>
     </row>
-    <row r="14" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2">
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="20">
         <v>2020</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -1765,22 +1762,22 @@
       <c r="M14" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="N14" s="18">
+      <c r="N14" s="17">
         <v>6</v>
       </c>
       <c r="O14" s="3"/>
     </row>
-    <row r="15" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="9">
         <v>12</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="21">
         <v>2021</v>
       </c>
       <c r="E15" s="11" t="s">
@@ -1810,22 +1807,22 @@
       <c r="M15" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="N15" s="18">
+      <c r="N15" s="17">
         <v>8</v>
       </c>
       <c r="O15" s="3"/>
     </row>
-    <row r="16" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="20">
         <v>2019</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -1855,22 +1852,22 @@
       <c r="M16" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="N16" s="18">
+      <c r="N16" s="17">
         <v>4</v>
       </c>
       <c r="O16" s="3"/>
     </row>
-    <row r="17" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2">
         <v>14</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="21">
         <v>2024</v>
       </c>
       <c r="E17" s="11" t="s">
@@ -1900,22 +1897,22 @@
       <c r="M17" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="N17" s="18">
+      <c r="N17" s="17">
         <v>2</v>
       </c>
       <c r="O17" s="3"/>
     </row>
-    <row r="18" spans="1:15" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="12">
+    <row r="18" spans="1:15" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="2">
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="20">
         <v>2024</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -1945,22 +1942,22 @@
       <c r="M18" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="N18" s="18">
+      <c r="N18" s="17">
         <v>10</v>
       </c>
       <c r="O18" s="3"/>
     </row>
-    <row r="19" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2">
         <v>16</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="21">
         <v>2024</v>
       </c>
       <c r="E19" s="11" t="s">
@@ -1990,22 +1987,22 @@
       <c r="M19" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="N19" s="18">
+      <c r="N19" s="17">
         <v>2</v>
       </c>
       <c r="O19" s="3"/>
     </row>
-    <row r="20" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2">
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="20">
         <v>2024</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -2035,7 +2032,7 @@
       <c r="M20" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="N20" s="18">
+      <c r="N20" s="17">
         <v>8</v>
       </c>
       <c r="O20" s="3"/>
